--- a/tabla_isr.xlsx
+++ b/tabla_isr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanj\Documentos\Sistema Fiscal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD46F47-1395-4416-99BD-953DF8565235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1849AB45-263C-4BB0-B558-0BEEEDCCF414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" firstSheet="2" activeTab="6" xr2:uid="{478D839A-8F10-435D-A675-280276A9862A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{478D839A-8F10-435D-A675-280276A9862A}"/>
   </bookViews>
   <sheets>
     <sheet name="Diaria" sheetId="1" r:id="rId1"/>
@@ -482,7 +482,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="1">
-        <v>1.9199999999999998E-2</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -496,7 +496,7 @@
         <v>0.53</v>
       </c>
       <c r="D3" s="1">
-        <v>6.4000000000000001E-2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -510,7 +510,7 @@
         <v>13.85</v>
       </c>
       <c r="D4" s="1">
-        <v>0.10879999999999999</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -524,7 +524,7 @@
         <v>33.28</v>
       </c>
       <c r="D5" s="1">
-        <v>0.16</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -538,7 +538,7 @@
         <v>44.05</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1792</v>
+        <v>17.920000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -552,7 +552,7 @@
         <v>61.08</v>
       </c>
       <c r="D7" s="1">
-        <v>0.21360000000000001</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -566,7 +566,7 @@
         <v>186.35</v>
       </c>
       <c r="D8" s="1">
-        <v>0.23519999999999999</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -580,7 +580,7 @@
         <v>343.98</v>
       </c>
       <c r="D9" s="1">
-        <v>0.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -594,7 +594,7 @@
         <v>844.05</v>
       </c>
       <c r="D10" s="1">
-        <v>0.32</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -608,7 +608,7 @@
         <v>1217.42</v>
       </c>
       <c r="D11" s="1">
-        <v>0.34</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -622,7 +622,7 @@
         <v>4391.07</v>
       </c>
       <c r="D12" s="1">
-        <v>0.35</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="1">
-        <v>1.9199999999999998E-2</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -680,7 +680,7 @@
         <v>3.71</v>
       </c>
       <c r="D3" s="1">
-        <v>6.4000000000000001E-2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -694,7 +694,7 @@
         <v>96.95</v>
       </c>
       <c r="D4" s="1">
-        <v>0.10879999999999999</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -708,7 +708,7 @@
         <v>232.96</v>
       </c>
       <c r="D5" s="1">
-        <v>0.16</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -722,7 +722,7 @@
         <v>308.35000000000002</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1792</v>
+        <v>17.920000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -736,7 +736,7 @@
         <v>427.56</v>
       </c>
       <c r="D7" s="1">
-        <v>0.21360000000000001</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -750,7 +750,7 @@
         <v>1304.45</v>
       </c>
       <c r="D8" s="1">
-        <v>0.23519999999999999</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -764,7 +764,7 @@
         <v>2407.86</v>
       </c>
       <c r="D9" s="1">
-        <v>0.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -778,7 +778,7 @@
         <v>5908.35</v>
       </c>
       <c r="D10" s="1">
-        <v>0.32</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -792,7 +792,7 @@
         <v>8521.94</v>
       </c>
       <c r="D11" s="1">
-        <v>0.34</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -806,7 +806,7 @@
         <v>30737.49</v>
       </c>
       <c r="D12" s="1">
-        <v>0.35</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -850,7 +850,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="1">
-        <v>1.9199999999999998E-2</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -864,7 +864,7 @@
         <v>5.3</v>
       </c>
       <c r="D3" s="1">
-        <v>6.4000000000000001E-2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -878,7 +878,7 @@
         <v>138.5</v>
       </c>
       <c r="D4" s="1">
-        <v>0.10879999999999999</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -892,7 +892,7 @@
         <v>332.8</v>
       </c>
       <c r="D5" s="1">
-        <v>0.16</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -906,7 +906,7 @@
         <v>440.5</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1792</v>
+        <v>17.920000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -920,7 +920,7 @@
         <v>610.79999999999995</v>
       </c>
       <c r="D7" s="1">
-        <v>0.21360000000000001</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -934,7 +934,7 @@
         <v>1863.5</v>
       </c>
       <c r="D8" s="1">
-        <v>0.23519999999999999</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -948,7 +948,7 @@
         <v>3439.8</v>
       </c>
       <c r="D9" s="1">
-        <v>0.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -962,7 +962,7 @@
         <v>8440.5</v>
       </c>
       <c r="D10" s="1">
-        <v>0.32</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -976,7 +976,7 @@
         <v>12174.2</v>
       </c>
       <c r="D11" s="1">
-        <v>0.34</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -990,7 +990,7 @@
         <v>43910.7</v>
       </c>
       <c r="D12" s="1">
-        <v>0.35</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1034,7 +1034,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="1">
-        <v>1.9199999999999998E-2</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -1048,7 +1048,7 @@
         <v>7.95</v>
       </c>
       <c r="D3" s="1">
-        <v>6.4000000000000001E-2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -1062,7 +1062,7 @@
         <v>207.75</v>
       </c>
       <c r="D4" s="1">
-        <v>0.10879999999999999</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -1076,7 +1076,7 @@
         <v>499.2</v>
       </c>
       <c r="D5" s="1">
-        <v>0.16</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -1090,7 +1090,7 @@
         <v>660.75</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1792</v>
+        <v>17.920000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -1104,7 +1104,7 @@
         <v>916.2</v>
       </c>
       <c r="D7" s="1">
-        <v>0.21360000000000001</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -1118,7 +1118,7 @@
         <v>2795.25</v>
       </c>
       <c r="D8" s="1">
-        <v>0.23519999999999999</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -1132,7 +1132,7 @@
         <v>5159.7</v>
       </c>
       <c r="D9" s="1">
-        <v>0.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -1146,7 +1146,7 @@
         <v>12660.75</v>
       </c>
       <c r="D10" s="1">
-        <v>0.32</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -1160,7 +1160,7 @@
         <v>18261.3</v>
       </c>
       <c r="D11" s="1">
-        <v>0.34</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -1174,7 +1174,7 @@
         <v>65866.05</v>
       </c>
       <c r="D12" s="1">
-        <v>0.35</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="1">
-        <v>1.9199999999999998E-2</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -1232,7 +1232,7 @@
         <v>16.22</v>
       </c>
       <c r="D3" s="1">
-        <v>6.4000000000000001E-2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -1246,7 +1246,7 @@
         <v>420.95</v>
       </c>
       <c r="D4" s="1">
-        <v>0.10879999999999999</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -1260,7 +1260,7 @@
         <v>1011.68</v>
       </c>
       <c r="D5" s="1">
-        <v>0.16</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -1274,7 +1274,7 @@
         <v>1339.14</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1792</v>
+        <v>17.920000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -1288,7 +1288,7 @@
         <v>1856.84</v>
       </c>
       <c r="D7" s="1">
-        <v>0.21360000000000001</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -1302,7 +1302,7 @@
         <v>5665.16</v>
       </c>
       <c r="D8" s="1">
-        <v>0.23519999999999999</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -1316,7 +1316,7 @@
         <v>10457.09</v>
       </c>
       <c r="D9" s="1">
-        <v>0.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -1330,7 +1330,7 @@
         <v>25659.23</v>
       </c>
       <c r="D10" s="1">
-        <v>0.32</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -1344,7 +1344,7 @@
         <v>37009.69</v>
       </c>
       <c r="D11" s="1">
-        <v>0.34</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -1358,7 +1358,7 @@
         <v>133488.54</v>
       </c>
       <c r="D12" s="1">
-        <v>0.35</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1402,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="1">
-        <v>1.9199999999999998E-2</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -1416,7 +1416,7 @@
         <v>32.44</v>
       </c>
       <c r="D3" s="1">
-        <v>6.4000000000000001E-2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -1430,7 +1430,7 @@
         <v>841.9</v>
       </c>
       <c r="D4" s="1">
-        <v>0.10879999999999999</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -1444,7 +1444,7 @@
         <v>2023.36</v>
       </c>
       <c r="D5" s="1">
-        <v>0.16</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -1458,7 +1458,7 @@
         <v>2678.28</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1792</v>
+        <v>17.920000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -1472,7 +1472,7 @@
         <v>3713.68</v>
       </c>
       <c r="D7" s="1">
-        <v>0.21360000000000001</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -1486,7 +1486,7 @@
         <v>11330.32</v>
       </c>
       <c r="D8" s="1">
-        <v>0.23519999999999999</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -1500,7 +1500,7 @@
         <v>20914.18</v>
       </c>
       <c r="D9" s="1">
-        <v>0.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -1514,7 +1514,7 @@
         <v>51318.46</v>
       </c>
       <c r="D10" s="1">
-        <v>0.32</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -1528,7 +1528,7 @@
         <v>74019.38</v>
       </c>
       <c r="D11" s="1">
-        <v>0.34</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -1542,7 +1542,7 @@
         <v>266977.08</v>
       </c>
       <c r="D12" s="1">
-        <v>0.35</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1585,8 +1585,8 @@
       <c r="C2" s="2">
         <v>0</v>
       </c>
-      <c r="D2" s="2">
-        <v>1.9199999999999998E-2</v>
+      <c r="D2" s="1">
+        <v>1.92</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -1599,8 +1599,8 @@
       <c r="C3" s="1">
         <v>194.59</v>
       </c>
-      <c r="D3" s="2">
-        <v>6.4000000000000001E-2</v>
+      <c r="D3" s="1">
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -1613,8 +1613,8 @@
       <c r="C4" s="1">
         <v>5051.37</v>
       </c>
-      <c r="D4" s="2">
-        <v>0.10879999999999999</v>
+      <c r="D4" s="1">
+        <v>10.88</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -1627,8 +1627,8 @@
       <c r="C5" s="1">
         <v>12140.13</v>
       </c>
-      <c r="D5" s="2">
-        <v>0.16</v>
+      <c r="D5" s="1">
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -1641,8 +1641,8 @@
       <c r="C6" s="1">
         <v>16069.64</v>
       </c>
-      <c r="D6" s="2">
-        <v>0.1792</v>
+      <c r="D6" s="1">
+        <v>17.920000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -1655,8 +1655,8 @@
       <c r="C7" s="1">
         <v>22282.14</v>
       </c>
-      <c r="D7" s="2">
-        <v>0.21360000000000001</v>
+      <c r="D7" s="1">
+        <v>21.36</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -1669,8 +1669,8 @@
       <c r="C8" s="1">
         <v>67981.919999999998</v>
       </c>
-      <c r="D8" s="2">
-        <v>0.23519999999999999</v>
+      <c r="D8" s="1">
+        <v>23.52</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -1683,8 +1683,8 @@
       <c r="C9" s="1">
         <v>125485.07</v>
       </c>
-      <c r="D9" s="2">
-        <v>0.3</v>
+      <c r="D9" s="1">
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -1697,8 +1697,8 @@
       <c r="C10" s="1">
         <v>307910.81</v>
       </c>
-      <c r="D10" s="2">
-        <v>0.32</v>
+      <c r="D10" s="1">
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -1711,8 +1711,8 @@
       <c r="C11" s="1">
         <v>444116.23</v>
       </c>
-      <c r="D11" s="2">
-        <v>0.34</v>
+      <c r="D11" s="1">
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -1725,8 +1725,8 @@
       <c r="C12" s="1">
         <v>1601862.46</v>
       </c>
-      <c r="D12" s="2">
-        <v>0.35</v>
+      <c r="D12" s="1">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/tabla_isr.xlsx
+++ b/tabla_isr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanj\Documentos\Sistema Fiscal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1849AB45-263C-4BB0-B558-0BEEEDCCF414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F132C1-110D-4122-A455-BFB237E129E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{478D839A-8F10-435D-A675-280276A9862A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{478D839A-8F10-435D-A675-280276A9862A}"/>
   </bookViews>
   <sheets>
     <sheet name="Diaria" sheetId="1" r:id="rId1"/>
